--- a/resources/学生信息表样表.xlsx
+++ b/resources/学生信息表样表.xlsx
@@ -1,365 +1,179 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="29868" windowHeight="13380" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$E$26</definedName>
+  </definedNames>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="55">
-  <si>
-    <t>序号</t>
-  </si>
-  <si>
-    <t>学生姓名</t>
-  </si>
-  <si>
-    <t>籍贯</t>
-  </si>
-  <si>
-    <t>班级</t>
-  </si>
-  <si>
-    <t>张三</t>
-  </si>
-  <si>
-    <t>广东广州</t>
-  </si>
-  <si>
-    <t>2602专门3班</t>
-  </si>
-  <si>
-    <t>李四</t>
-  </si>
-  <si>
-    <t>广东汕头</t>
-  </si>
-  <si>
-    <t>王五</t>
-  </si>
-  <si>
-    <t>广东韶关</t>
-  </si>
-  <si>
-    <t>赵六</t>
-  </si>
-  <si>
-    <t>湖南衡阳</t>
-  </si>
-  <si>
-    <t>张吉惟</t>
-  </si>
-  <si>
-    <t>湖南长沙</t>
-  </si>
-  <si>
-    <t>林国瑞</t>
-  </si>
-  <si>
-    <t>湖南娄底</t>
-  </si>
-  <si>
-    <t>林玟书</t>
-  </si>
-  <si>
-    <t>江西南昌</t>
-  </si>
-  <si>
-    <t>林雅南</t>
-  </si>
-  <si>
-    <t>江西九江</t>
-  </si>
-  <si>
-    <t>江奕云</t>
-  </si>
-  <si>
-    <t>江西赣州</t>
-  </si>
-  <si>
-    <t>刘柏宏</t>
-  </si>
-  <si>
-    <t>湖北荆州</t>
-  </si>
-  <si>
-    <t>阮建安</t>
-  </si>
-  <si>
-    <t>湖北武汉</t>
-  </si>
-  <si>
-    <t>林子帆</t>
-  </si>
-  <si>
-    <t>湖北梅县</t>
-  </si>
-  <si>
-    <t>夏志豪</t>
-  </si>
-  <si>
-    <t>黑龙江哈尔滨</t>
-  </si>
-  <si>
-    <t>吉茹定</t>
-  </si>
-  <si>
-    <t>黑龙江齐齐哈尔市</t>
-  </si>
-  <si>
-    <t>李中冰</t>
-  </si>
-  <si>
-    <t>黑龙江大庆市</t>
-  </si>
-  <si>
-    <t>黄文隆</t>
-  </si>
-  <si>
-    <t>浙江杭州</t>
-  </si>
-  <si>
-    <t>谢彦文</t>
-  </si>
-  <si>
-    <t>浙江衢州</t>
-  </si>
-  <si>
-    <t>傅智翔</t>
-  </si>
-  <si>
-    <t>浙江宁波</t>
-  </si>
-  <si>
-    <t>洪振霞</t>
-  </si>
-  <si>
-    <t>陕西宝鸡</t>
-  </si>
-  <si>
-    <t>刘姿婷</t>
-  </si>
-  <si>
-    <t>陕西铜川</t>
-  </si>
-  <si>
-    <t>荣姿康</t>
-  </si>
-  <si>
-    <t>陕西安康</t>
-  </si>
-  <si>
-    <t>吕致盈</t>
-  </si>
-  <si>
-    <t>山西太原</t>
-  </si>
-  <si>
-    <t>方一强</t>
-  </si>
-  <si>
-    <t>山西大同</t>
-  </si>
-  <si>
-    <t>黎芸贵</t>
-  </si>
-  <si>
-    <t>山西吕梁</t>
-  </si>
-  <si>
-    <t>郑伊</t>
-  </si>
-  <si>
-    <t>山西朔州</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+      <color rgb="FF006100"/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF9C0006"/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
+      <color rgb="FF9C6500"/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color theme="0"/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -659,161 +473,162 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1059,7 +874,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -1068,7 +883,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -1081,11 +896,74 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1337,381 +1215,573 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultColWidth="8.73148148148148" defaultRowHeight="14.4" outlineLevelCol="3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E26"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.731481481481479" defaultRowHeight="14.4"/>
   <cols>
-    <col min="3" max="3" width="18.5462962962963" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
+    <col width="18.5462962962963" customWidth="1" style="2" min="3" max="3"/>
+    <col width="13" customWidth="1" style="2" min="4" max="4"/>
+    <col width="22" customWidth="1" style="2" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>学生姓名</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>籍贯</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>班级</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>送生区</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>广东广州</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>2602专门3班</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>广东汕头</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>2602专门3班</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>广东韶关</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>2602专门3班</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>湖南衡阳</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>2602专门3班</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>张吉惟</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>湖南长沙</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>2602专门3班</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>林国瑞</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>湖南娄底</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>2602专门3班</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>林玟书</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>江西南昌</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>2602专门3班</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>林雅南</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>江西九江</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>2602专门3班</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>江奕云</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>江西赣州</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>2602专门3班</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="D4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>刘柏宏</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>湖北荆州</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>2602专门3班</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>阮建安</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>湖北武汉</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>2602专门3班</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>林子帆</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>湖北梅县</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>2602专门3班</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>夏志豪</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>黑龙江哈尔滨</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>2602专门3班</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="D6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>吉茹定</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>黑龙江齐齐哈尔市</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>2602专门3班</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>李中冰</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>黑龙江大庆市</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>2602专门3班</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="D7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>黄文隆</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>浙江杭州</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>2602专门3班</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>谢彦文</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>浙江衢州</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>2602专门3班</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="n">
         <v>18</v>
       </c>
-      <c r="D8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>傅智翔</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>浙江宁波</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>2602专门3班</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>洪振霞</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>陕西宝鸡</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>2602专门3班</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="D9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>刘姿婷</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>陕西铜川</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>2602专门3班</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="n">
         <v>21</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>荣姿康</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>陕西安康</t>
+        </is>
+      </c>
+      <c r="D22" s="0" t="inlineStr">
+        <is>
+          <t>2602专门3班</t>
+        </is>
+      </c>
+      <c r="E22" s="0" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="n">
         <v>22</v>
       </c>
-      <c r="D10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t>吕致盈</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>山西太原</t>
+        </is>
+      </c>
+      <c r="D23" s="0" t="inlineStr">
+        <is>
+          <t>2602专门3班</t>
+        </is>
+      </c>
+      <c r="E23" s="0" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="n">
         <v>23</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>方一强</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t>山西大同</t>
+        </is>
+      </c>
+      <c r="D24" s="0" t="inlineStr">
+        <is>
+          <t>2602专门3班</t>
+        </is>
+      </c>
+      <c r="E24" s="0" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="n">
         <v>24</v>
       </c>
-      <c r="D11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>黎芸贵</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>山西吕梁</t>
+        </is>
+      </c>
+      <c r="D25" s="0" t="inlineStr">
+        <is>
+          <t>2602专门3班</t>
+        </is>
+      </c>
+      <c r="E25" s="0" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="n">
         <v>25</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D17" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D18" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D19" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D20" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D23" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25" t="s">
-        <v>51</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D25" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D26" t="s">
-        <v>6</v>
-      </c>
+      <c r="B26" s="0" t="inlineStr">
+        <is>
+          <t>郑伊</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="inlineStr">
+        <is>
+          <t>山西朔州</t>
+        </is>
+      </c>
+      <c r="D26" s="0" t="inlineStr">
+        <is>
+          <t>2602专门3班</t>
+        </is>
+      </c>
+      <c r="E26" s="0" t="n"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>